--- a/artfynd/A 31525-2026 artfynd.xlsx
+++ b/artfynd/A 31525-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135352558</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58250</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Riseberga ek/hasselskog, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>396085</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6214332</v>
+      </c>
+      <c r="S3" t="n">
+        <v>40</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135352538</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58134</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Riseberga ek/hasselskog, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>396085</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6214332</v>
+      </c>
+      <c r="S4" t="n">
+        <v>40</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31525-2026 artfynd.xlsx
+++ b/artfynd/A 31525-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113009506</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135352558</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -988,8 +1003,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135352538</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31525-2026 artfynd.xlsx
+++ b/artfynd/A 31525-2026 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>135352558</v>
       </c>
       <c r="B3" t="n">
-        <v>58250</v>
+        <v>58255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,7 +900,7 @@
         <v>135352538</v>
       </c>
       <c r="B4" t="n">
-        <v>58134</v>
+        <v>58139</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 31525-2026 artfynd.xlsx
+++ b/artfynd/A 31525-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ2"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -785,9 +785,235 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>135352558</v>
+      </c>
+      <c r="B3" t="n">
+        <v>58255</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103019</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stjärtmes</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Aegithalos caudatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Riseberga ek/hasselskog, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>396085</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6214332</v>
+      </c>
+      <c r="S3" t="n">
+        <v>40</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135352558</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>135352538</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58139</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103020</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Entita</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Poecile palustris</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Riseberga ek/hasselskog, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>396085</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6214332</v>
+      </c>
+      <c r="S4" t="n">
+        <v>40</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Klippan</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Riseberga</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Petra Borgcrantz</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135352538</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
